--- a/cet4/result/82_医道女神_生命守护的仁心/82_医道女神_生命守护的仁心_学习版.xlsx
+++ b/cet4/result/82_医道女神_生命守护的仁心/82_医道女神_生命守护的仁心_学习版.xlsx
@@ -397,1207 +397,745 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D52"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>yesterday</v>
       </c>
       <c r="B2" t="str">
-        <v>yesterday</v>
+        <v>/ˈjestədeɪ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D2" t="str">
         <v>昨天</v>
       </c>
-      <c r="D2" t="str">
-        <v>yesterday(昨天)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>area</v>
       </c>
       <c r="B3" t="str">
-        <v>area</v>
+        <v>/ˈeriə/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>区域</v>
       </c>
-      <c r="D3" t="str">
-        <v>area(区域)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>career</v>
       </c>
       <c r="B4" t="str">
-        <v>career</v>
+        <v>/kəˈrɪr/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vi./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>事业</v>
       </c>
-      <c r="D4" t="str">
-        <v>career(事业)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>father</v>
       </c>
       <c r="B5" t="str">
-        <v>father</v>
+        <v>/ˈfɑːðər/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D5" t="str">
         <v>父亲</v>
       </c>
-      <c r="D5" t="str">
-        <v>father(父亲)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>must</v>
       </c>
       <c r="B6" t="str">
-        <v>must</v>
+        <v>/məst,mʌst/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./aux.</v>
+      </c>
+      <c r="D6" t="str">
         <v>必须</v>
       </c>
-      <c r="D6" t="str">
-        <v>must(必须)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>pupil</v>
       </c>
       <c r="B7" t="str">
-        <v>pupil</v>
+        <v>/ˈpjuːpl/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>学生</v>
       </c>
-      <c r="D7" t="str">
-        <v>pupil(学生)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>command</v>
       </c>
       <c r="B8" t="str">
-        <v>command</v>
+        <v>/kəˈmænd/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>命令</v>
       </c>
-      <c r="D8" t="str">
-        <v>command(命令)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>closely</v>
       </c>
       <c r="B9" t="str">
-        <v>area</v>
+        <v>/ˈkloʊsli/</v>
       </c>
       <c r="C9" t="str">
-        <v>区域</v>
+        <v>v./adv.</v>
       </c>
       <c r="D9" t="str">
-        <v>area(区域)📢</v>
+        <v>密切地</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>organism</v>
       </c>
       <c r="B10" t="str">
-        <v>closely</v>
+        <v>/ˈɔːrɡənɪzəm/</v>
       </c>
       <c r="C10" t="str">
-        <v>密切地</v>
+        <v>n.</v>
       </c>
       <c r="D10" t="str">
-        <v>closely(密切地)📢</v>
+        <v>机体</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>agony</v>
       </c>
       <c r="B11" t="str">
-        <v>organism</v>
+        <v>/ˈæɡəni/</v>
       </c>
       <c r="C11" t="str">
-        <v>机体</v>
+        <v>n.</v>
       </c>
       <c r="D11" t="str">
-        <v>organism(机体)📢</v>
+        <v>痛苦</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>ourselves</v>
       </c>
       <c r="B12" t="str">
-        <v>agony</v>
+        <v>/ɑːˈselvz/</v>
       </c>
       <c r="C12" t="str">
-        <v>痛苦</v>
+        <v>n./pron.</v>
       </c>
       <c r="D12" t="str">
-        <v>agony(痛苦)📢</v>
+        <v>我们自己</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>sensible</v>
       </c>
       <c r="B13" t="str">
-        <v>yesterday</v>
+        <v>/ˈsensəbl/</v>
       </c>
       <c r="C13" t="str">
-        <v>昨天</v>
+        <v>n./adj.</v>
       </c>
       <c r="D13" t="str">
-        <v>yesterday(昨天)📢</v>
+        <v>明智的</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>grandson</v>
       </c>
       <c r="B14" t="str">
-        <v>ourselves</v>
+        <v>/ˈɡrænsʌn/</v>
       </c>
       <c r="C14" t="str">
-        <v>我们自己</v>
+        <v>n.</v>
       </c>
       <c r="D14" t="str">
-        <v>ourselves(我们自己)📢</v>
+        <v>孙子</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>modest</v>
       </c>
       <c r="B15" t="str">
-        <v>sensible</v>
+        <v>/ˈmɑːdɪst/</v>
       </c>
       <c r="C15" t="str">
-        <v>明智的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D15" t="str">
-        <v>sensible(明智的)📢</v>
+        <v>谦逊的</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>interior</v>
       </c>
       <c r="B16" t="str">
-        <v>grandson</v>
+        <v>/ɪnˈtɪriər/</v>
       </c>
       <c r="C16" t="str">
-        <v>孙子</v>
+        <v>n./adj.</v>
       </c>
       <c r="D16" t="str">
-        <v>grandson(孙子)📢</v>
+        <v>内部</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>sufficient</v>
       </c>
       <c r="B17" t="str">
-        <v>modest</v>
+        <v>/səˈfɪʃnt/</v>
       </c>
       <c r="C17" t="str">
-        <v>谦逊的</v>
+        <v>adj.</v>
       </c>
       <c r="D17" t="str">
-        <v>modest(谦逊的)📢</v>
+        <v>充足的</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>adequate</v>
       </c>
       <c r="B18" t="str">
-        <v>interior</v>
+        <v>/ˈædɪkwət/</v>
       </c>
       <c r="C18" t="str">
-        <v>内部</v>
+        <v>adj.</v>
       </c>
       <c r="D18" t="str">
-        <v>interior(内部)📢</v>
+        <v>适当的</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>letter</v>
       </c>
       <c r="B19" t="str">
-        <v>sufficient</v>
+        <v>/ˈletər/</v>
       </c>
       <c r="C19" t="str">
-        <v>充足的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D19" t="str">
-        <v>sufficient(充足的)📢</v>
+        <v>信</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>roll</v>
       </c>
       <c r="B20" t="str">
-        <v>adequate</v>
+        <v>/roʊl/</v>
       </c>
       <c r="C20" t="str">
-        <v>适当的</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>adequate(适当的)📢</v>
+        <v>卷起</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>basket</v>
       </c>
       <c r="B21" t="str">
-        <v>letter</v>
+        <v>/ˈbæskɪt/</v>
       </c>
       <c r="C21" t="str">
-        <v>信</v>
+        <v>n./vt.</v>
       </c>
       <c r="D21" t="str">
-        <v>letter(信)📢</v>
+        <v>篮子</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>column</v>
       </c>
       <c r="B22" t="str">
-        <v>yesterday</v>
+        <v>/ˈkɑːləm/</v>
       </c>
       <c r="C22" t="str">
-        <v>昨天</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>yesterday(昨天)📰</v>
+        <v>专栏</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>productive</v>
       </c>
       <c r="B23" t="str">
-        <v>roll</v>
+        <v>/prəˈdʌktɪv/</v>
       </c>
       <c r="C23" t="str">
-        <v>卷起</v>
+        <v>adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>roll(卷起)📢</v>
+        <v>富有成效的</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>solemn</v>
       </c>
       <c r="B24" t="str">
-        <v>basket</v>
+        <v>/ˈsɑːləm/</v>
       </c>
       <c r="C24" t="str">
-        <v>篮子</v>
+        <v>adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>basket(篮子)📢</v>
+        <v>庄严的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>section</v>
       </c>
       <c r="B25" t="str">
-        <v>basket</v>
+        <v>/ˈsekʃn/</v>
       </c>
       <c r="C25" t="str">
-        <v>篮子</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>basket(篮子)📢</v>
+        <v>部分</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>comment</v>
       </c>
       <c r="B26" t="str">
-        <v>column</v>
+        <v>/ˈkɑːment/</v>
       </c>
       <c r="C26" t="str">
-        <v>专栏</v>
+        <v>n./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>column(专栏)📢</v>
+        <v>评论</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>slowly</v>
       </c>
       <c r="B27" t="str">
-        <v>productive</v>
+        <v>/ˈsloʊli/</v>
       </c>
       <c r="C27" t="str">
-        <v>富有成效的</v>
+        <v>v./adv.</v>
       </c>
       <c r="D27" t="str">
-        <v>productive(富有成效的)📢</v>
+        <v>慢慢地</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>upset</v>
       </c>
       <c r="B28" t="str">
-        <v>must</v>
+        <v>/ʌpˈset/</v>
       </c>
       <c r="C28" t="str">
-        <v>必须</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>must(必须)📢</v>
+        <v>心烦</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>prospect</v>
       </c>
       <c r="B29" t="str">
-        <v>solemn</v>
+        <v>/ˈprɑːspekt/</v>
       </c>
       <c r="C29" t="str">
-        <v>庄严的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>solemn(庄严的)📢</v>
+        <v>前景</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>both</v>
       </c>
       <c r="B30" t="str">
-        <v>section</v>
+        <v>/boʊθ/</v>
       </c>
       <c r="C30" t="str">
-        <v>部分</v>
+        <v>n./v./adv./pron./conj.</v>
       </c>
       <c r="D30" t="str">
-        <v>section(部分)📢</v>
+        <v>双方</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>conscious</v>
       </c>
       <c r="B31" t="str">
-        <v>comment</v>
+        <v>/ˈkɑːnʃəs/</v>
       </c>
       <c r="C31" t="str">
-        <v>评论</v>
+        <v>adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>comment(评论)📢</v>
+        <v>意识到的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>company</v>
       </c>
       <c r="B32" t="str">
-        <v>slowly</v>
+        <v>/ˈkʌmpəni/</v>
       </c>
       <c r="C32" t="str">
-        <v>慢慢地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>slowly(慢慢地)📢</v>
+        <v>陪伴</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>confess</v>
       </c>
       <c r="B33" t="str">
-        <v>upset</v>
+        <v>/kənˈfes/</v>
       </c>
       <c r="C33" t="str">
-        <v>心烦</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>upset(心烦)📢</v>
+        <v>承认</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>somewhere</v>
       </c>
       <c r="B34" t="str">
-        <v>prospect</v>
+        <v>/ˈsʌmwer/</v>
       </c>
       <c r="C34" t="str">
-        <v>前景</v>
+        <v>n./v./adv.</v>
       </c>
       <c r="D34" t="str">
-        <v>prospect(前景)📢</v>
+        <v>某处</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>bear</v>
       </c>
       <c r="B35" t="str">
-        <v>both</v>
+        <v>/ber/</v>
       </c>
       <c r="C35" t="str">
-        <v>双方</v>
+        <v>n./v.</v>
       </c>
       <c r="D35" t="str">
-        <v>both(双方)📢</v>
+        <v>承担</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>flag</v>
       </c>
       <c r="B36" t="str">
-        <v>conscious</v>
+        <v>/flæɡ/</v>
       </c>
       <c r="C36" t="str">
-        <v>意识到的</v>
+        <v>n./v.</v>
       </c>
       <c r="D36" t="str">
-        <v>conscious(意识到的)📢</v>
+        <v>旗帜</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>underneath</v>
       </c>
       <c r="B37" t="str">
-        <v>company</v>
+        <v>/ˌʌndərˈniːθ/</v>
       </c>
       <c r="C37" t="str">
-        <v>陪伴</v>
+        <v>v./adv./prep.</v>
       </c>
       <c r="D37" t="str">
-        <v>company(陪伴)📢</v>
+        <v>下面</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>hear</v>
       </c>
       <c r="B38" t="str">
-        <v>confess</v>
+        <v>/hɪr/</v>
       </c>
       <c r="C38" t="str">
-        <v>承认</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>confess(承认)📢</v>
+        <v>听到</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>nylon</v>
       </c>
       <c r="B39" t="str">
-        <v>somewhere</v>
+        <v>/ˈnaɪlɑːn/</v>
       </c>
       <c r="C39" t="str">
-        <v>某处</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>somewhere(某处)📢</v>
+        <v>尼龙</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>sweater</v>
       </c>
       <c r="B40" t="str">
-        <v>father</v>
+        <v>/ˈswetər/</v>
       </c>
       <c r="C40" t="str">
-        <v>父亲</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>father(父亲)📰</v>
+        <v>毛衣</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>gauge</v>
       </c>
       <c r="B41" t="str">
-        <v>bear</v>
+        <v>/ɡeɪdʒ/</v>
       </c>
       <c r="C41" t="str">
-        <v>承担</v>
+        <v>n./vt.</v>
       </c>
       <c r="D41" t="str">
-        <v>bear(承担)📢</v>
+        <v>测量</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>chin</v>
       </c>
       <c r="B42" t="str">
-        <v>flag</v>
+        <v>/tʃɪn/</v>
       </c>
       <c r="C42" t="str">
-        <v>旗帜</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>flag(旗帜)📢</v>
+        <v>下巴</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>comparison</v>
       </c>
       <c r="B43" t="str">
-        <v>flag</v>
+        <v>/kəmˈpærɪsn/</v>
       </c>
       <c r="C43" t="str">
-        <v>旗帜</v>
+        <v>n.</v>
       </c>
       <c r="D43" t="str">
-        <v>flag(旗帜)📢</v>
+        <v>比较</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>luck</v>
       </c>
       <c r="B44" t="str">
-        <v>underneath</v>
+        <v>/lʌk/</v>
       </c>
       <c r="C44" t="str">
-        <v>下面</v>
+        <v>n./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>underneath(下面)📢</v>
+        <v>运气</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>fleet</v>
       </c>
       <c r="B45" t="str">
-        <v>hear</v>
+        <v>/fliːt/</v>
       </c>
       <c r="C45" t="str">
-        <v>听到</v>
+        <v>n./vt./vi./v./adj./adv.</v>
       </c>
       <c r="D45" t="str">
-        <v>hear(听到)📢</v>
+        <v>车队</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>await</v>
       </c>
       <c r="B46" t="str">
-        <v>solemn</v>
+        <v>/əˈweɪt/</v>
       </c>
       <c r="C46" t="str">
-        <v>庄严的</v>
+        <v>vt.</v>
       </c>
       <c r="D46" t="str">
-        <v>solemn(庄严的)📢</v>
+        <v>等待</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>shut</v>
       </c>
       <c r="B47" t="str">
-        <v>nylon</v>
+        <v>/ʃʌt/</v>
       </c>
       <c r="C47" t="str">
-        <v>尼龙</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>nylon(尼龙)📢</v>
+        <v>关上</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>dread</v>
       </c>
       <c r="B48" t="str">
-        <v>sweater</v>
+        <v>/dred/</v>
       </c>
       <c r="C48" t="str">
-        <v>毛衣</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>sweater(毛衣)📢</v>
+        <v>恐惧</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>confirm</v>
       </c>
       <c r="B49" t="str">
-        <v>gauge</v>
+        <v>/kənˈfɜːrm/</v>
       </c>
       <c r="C49" t="str">
-        <v>测量</v>
+        <v>vt.</v>
       </c>
       <c r="D49" t="str">
-        <v>gauge(测量)📢</v>
+        <v>确认</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>taste</v>
       </c>
       <c r="B50" t="str">
-        <v>chin</v>
+        <v>/teɪst/</v>
       </c>
       <c r="C50" t="str">
-        <v>下巴</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>chin(下巴)📢</v>
+        <v>品尝</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>onto</v>
       </c>
       <c r="B51" t="str">
-        <v>area</v>
+        <v>/ˈɑːntə,ˈɑːntu/</v>
       </c>
       <c r="C51" t="str">
-        <v>区域</v>
+        <v>prep.</v>
       </c>
       <c r="D51" t="str">
-        <v>area(区域)📢</v>
+        <v>在...之上</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>anyone</v>
       </c>
       <c r="B52" t="str">
-        <v>comparison</v>
+        <v>/ˈeniwʌn/</v>
       </c>
       <c r="C52" t="str">
-        <v>比较</v>
+        <v>n./pron.</v>
       </c>
       <c r="D52" t="str">
-        <v>comparison(比较)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>luck</v>
-      </c>
-      <c r="C53" t="str">
-        <v>运气</v>
-      </c>
-      <c r="D53" t="str">
-        <v>luck(运气)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>fleet</v>
-      </c>
-      <c r="C54" t="str">
-        <v>车队</v>
-      </c>
-      <c r="D54" t="str">
-        <v>fleet(车队)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>await</v>
-      </c>
-      <c r="C55" t="str">
-        <v>等待</v>
-      </c>
-      <c r="D55" t="str">
-        <v>await(等待)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>somewhere</v>
-      </c>
-      <c r="C56" t="str">
-        <v>某处</v>
-      </c>
-      <c r="D56" t="str">
-        <v>somewhere(某处)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>sufficient</v>
-      </c>
-      <c r="C57" t="str">
-        <v>充足的</v>
-      </c>
-      <c r="D57" t="str">
-        <v>sufficient(充足的)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>sensible</v>
-      </c>
-      <c r="C58" t="str">
-        <v>明智的</v>
-      </c>
-      <c r="D58" t="str">
-        <v>sensible(明智的)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>confess</v>
-      </c>
-      <c r="C59" t="str">
-        <v>坦白</v>
-      </c>
-      <c r="D59" t="str">
-        <v>confess(坦白)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>shut</v>
-      </c>
-      <c r="C60" t="str">
-        <v>关上</v>
-      </c>
-      <c r="D60" t="str">
-        <v>shut(关上)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>somewhere</v>
-      </c>
-      <c r="C61" t="str">
-        <v>某处</v>
-      </c>
-      <c r="D61" t="str">
-        <v>somewhere(某处)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>command</v>
-      </c>
-      <c r="C62" t="str">
-        <v>命令</v>
-      </c>
-      <c r="D62" t="str">
-        <v>command(命令)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>roll</v>
-      </c>
-      <c r="C63" t="str">
-        <v>滚动</v>
-      </c>
-      <c r="D63" t="str">
-        <v>roll(滚动)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>await</v>
-      </c>
-      <c r="C64" t="str">
-        <v>等待</v>
-      </c>
-      <c r="D64" t="str">
-        <v>await(等待)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>dread</v>
-      </c>
-      <c r="C65" t="str">
-        <v>恐惧</v>
-      </c>
-      <c r="D65" t="str">
-        <v>dread(恐惧)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>grandson</v>
-      </c>
-      <c r="C66" t="str">
-        <v>孙子</v>
-      </c>
-      <c r="D66" t="str">
-        <v>grandson(孙子)📰</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>closely</v>
-      </c>
-      <c r="C67" t="str">
-        <v>紧密地</v>
-      </c>
-      <c r="D67" t="str">
-        <v>closely(紧密地)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>organism</v>
-      </c>
-      <c r="C68" t="str">
-        <v>机体</v>
-      </c>
-      <c r="D68" t="str">
-        <v>organism(机体)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>confirm</v>
-      </c>
-      <c r="C69" t="str">
-        <v>确认</v>
-      </c>
-      <c r="D69" t="str">
-        <v>confirm(确认)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>taste</v>
-      </c>
-      <c r="C70" t="str">
-        <v>品尝</v>
-      </c>
-      <c r="D70" t="str">
-        <v>taste(品尝)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>agony</v>
-      </c>
-      <c r="C71" t="str">
-        <v>痛苦</v>
-      </c>
-      <c r="D71" t="str">
-        <v>agony(痛苦)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>luck</v>
-      </c>
-      <c r="C72" t="str">
-        <v>幸运</v>
-      </c>
-      <c r="D72" t="str">
-        <v>luck(幸运)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>modest</v>
-      </c>
-      <c r="C73" t="str">
-        <v>谦逊地</v>
-      </c>
-      <c r="D73" t="str">
-        <v>modest(谦逊地)📢</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>slowly</v>
-      </c>
-      <c r="C74" t="str">
-        <v>缓慢地</v>
-      </c>
-      <c r="D74" t="str">
-        <v>slowly(缓慢地)📢</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
-        <v>both</v>
-      </c>
-      <c r="C75" t="str">
-        <v>两者</v>
-      </c>
-      <c r="D75" t="str">
-        <v>both(两者)📢</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="str">
-        <v>career</v>
-      </c>
-      <c r="C76" t="str">
-        <v>事业</v>
-      </c>
-      <c r="D76" t="str">
-        <v>career(事业)📢</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="str">
-        <v>column</v>
-      </c>
-      <c r="C77" t="str">
-        <v>圆柱</v>
-      </c>
-      <c r="D77" t="str">
-        <v>column(圆柱)📢</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="str">
-        <v>area</v>
-      </c>
-      <c r="C78" t="str">
-        <v>区域</v>
-      </c>
-      <c r="D78" t="str">
-        <v>area(区域)📢</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="str">
-        <v>father</v>
-      </c>
-      <c r="C79" t="str">
-        <v>父亲</v>
-      </c>
-      <c r="D79" t="str">
-        <v>father(父亲)📢</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="str">
-        <v>productive</v>
-      </c>
-      <c r="C80" t="str">
-        <v>富有成效的</v>
-      </c>
-      <c r="D80" t="str">
-        <v>productive(富有成效的)📢</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="str">
-        <v>prospect</v>
-      </c>
-      <c r="C81" t="str">
-        <v>前途</v>
-      </c>
-      <c r="D81" t="str">
-        <v>prospect(前途)📢</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="str">
-        <v>flag</v>
-      </c>
-      <c r="C82" t="str">
-        <v>旗帜</v>
-      </c>
-      <c r="D82" t="str">
-        <v>flag(旗帜)📢</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="str">
-        <v>bear</v>
-      </c>
-      <c r="C83" t="str">
-        <v>承受</v>
-      </c>
-      <c r="D83" t="str">
-        <v>bear(承受)📢</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="str">
-        <v>onto</v>
-      </c>
-      <c r="C84" t="str">
-        <v>在...之上</v>
-      </c>
-      <c r="D84" t="str">
-        <v>onto(在...之上)📢</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="str">
-        <v>anyone</v>
-      </c>
-      <c r="C85" t="str">
         <v>任何人</v>
-      </c>
-      <c r="D85" t="str">
-        <v>anyone(任何人)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D85"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>